--- a/docs/test-data/scenarios/JetBlue_B6_Scenario_Seed_2026-09-24_to_26.xlsx
+++ b/docs/test-data/scenarios/JetBlue_B6_Scenario_Seed_2026-09-24_to_26.xlsx
@@ -2318,7 +2318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2371,6 +2371,7 @@
     <col width="21" customWidth="1" min="48" max="48"/>
     <col width="24" customWidth="1" min="49" max="49"/>
     <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="14" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2622,6 +2623,11 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>order_category</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>carrier_code</t>
         </is>
       </c>
     </row>
@@ -2808,6 +2814,11 @@
           <t>MAINTENANCE</t>
         </is>
       </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2992,6 +3003,11 @@
           <t>MAINTENANCE</t>
         </is>
       </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3174,6 +3190,11 @@
       <c r="AX4" t="inlineStr">
         <is>
           <t>MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>B6</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV4"/>
+  <dimension ref="A1:AW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3239,6 +3260,7 @@
     <col width="19" customWidth="1" min="46" max="46"/>
     <col width="21" customWidth="1" min="47" max="47"/>
     <col width="21" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3480,6 +3502,11 @@
       <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>flight_tolerance_kg</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>carrier_code</t>
         </is>
       </c>
     </row>
@@ -3664,6 +3691,11 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3846,6 +3878,11 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4028,6 +4065,11 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4040,7 +4082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4093,6 +4135,7 @@
     <col width="14" customWidth="1" min="48" max="48"/>
     <col width="12" customWidth="1" min="49" max="49"/>
     <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="14" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4344,6 +4387,11 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>s4_fi_posting_date</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>carrier_code</t>
         </is>
       </c>
     </row>
@@ -4542,6 +4590,11 @@
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4738,6 +4791,11 @@
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4930,6 +4988,11 @@
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5122,6 +5185,11 @@
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5314,6 +5382,11 @@
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8688,7 +8761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG8"/>
+  <dimension ref="A1:AH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8724,6 +8797,7 @@
     <col width="18" customWidth="1" min="31" max="31"/>
     <col width="17" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8890,6 +8964,11 @@
       <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>charge_type</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>carrier_code</t>
         </is>
       </c>
     </row>
@@ -9019,6 +9098,11 @@
           <t>FUEL</t>
         </is>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9146,6 +9230,11 @@
           <t>FUEL</t>
         </is>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9273,6 +9362,11 @@
           <t>FUEL</t>
         </is>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9398,6 +9492,11 @@
       <c r="AG5" t="inlineStr">
         <is>
           <t>FUEL</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>B6</t>
         </is>
       </c>
     </row>
@@ -9523,6 +9622,11 @@
           <t>FUEL</t>
         </is>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9646,6 +9750,11 @@
           <t>FUEL</t>
         </is>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9767,6 +9876,11 @@
       <c r="AG8" t="inlineStr">
         <is>
           <t>FUEL</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>B6</t>
         </is>
       </c>
     </row>

--- a/docs/test-data/scenarios/JetBlue_B6_Scenario_Seed_2026-09-24_to_26.xlsx
+++ b/docs/test-data/scenarios/JetBlue_B6_Scenario_Seed_2026-09-24_to_26.xlsx
@@ -32605,7 +32605,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>NO - needs schema (proposed sheets)</t>
+          <t>PARTIAL - the defuel and its charge are seeded</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -32650,7 +32650,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Not demonstrable until movement type / DEFUEL_SERVICE charge exist. Data is ready in PROPOSED_DEFUEL_* sheets.</t>
+          <t>Defueling app: the defuel (TO_SUPPLIER, PARKED) carries the service charge in defuel_charges_usd. Matching the supplier's service invoice needs a DEFUEL_SERVICE charge type on invoice lines, which does not exist. Seeded by tools/seed-defuel-scenarios.js.</t>
         </is>
       </c>
     </row>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>NO - needs schema (proposed sheets)</t>
+          <t>PARTIAL - the defuel and its charge are seeded</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -32710,7 +32710,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Not demonstrable until movement type / DEFUEL_SERVICE charge exist. Data is ready in PROPOSED_DEFUEL_* sheets.</t>
+          <t>Defueling app: the defuel (TO_SUPPLIER, PARKED) carries the service charge in defuel_charges_usd. Matching the supplier's service invoice needs a DEFUEL_SERVICE charge type on invoice lines, which does not exist. Seeded by tools/seed-defuel-scenarios.js.</t>
         </is>
       </c>
     </row>
@@ -32725,7 +32725,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>NO - needs schema (proposed sheets)</t>
+          <t>PARTIAL - the defuel and its charge are seeded</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -32770,7 +32770,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Not demonstrable until movement type / DEFUEL_SERVICE charge exist. Data is ready in PROPOSED_DEFUEL_* sheets.</t>
+          <t>Defueling app: the defuel (TO_SUPPLIER, PARKED) carries the service charge in defuel_charges_usd. Matching the supplier's service invoice needs a DEFUEL_SERVICE charge type on invoice lines, which does not exist. Seeded by tools/seed-defuel-scenarios.js.</t>
         </is>
       </c>
     </row>
@@ -32785,7 +32785,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL - shows the gap</t>
+          <t>YES (B6) - expected credit; credit memo when that branch merges</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -32830,7 +32830,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Load the credit note as an invoice and Validate: INV456 HARD on the negative line (no field marks a defuel). Full demo needs document_type CREDIT_NOTE.</t>
+          <t>Defueling app: the defuel is posted to the supplier (POSTING_PENDING) with its expected credit; 12C credits 300 L less and writes the rest off. ExpectedCredits on the invoice service lists them. TP is not seeded: expected credits are USD-only in the credit memo R1.</t>
         </is>
       </c>
     </row>
@@ -32845,7 +32845,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL - shows the gap</t>
+          <t>YES (B6) - expected credit; credit memo when that branch merges</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -32890,7 +32890,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Load the credit note as an invoice and Validate: INV456 HARD on the negative line (no field marks a defuel). Full demo needs document_type CREDIT_NOTE.</t>
+          <t>Defueling app: the defuel is posted to the supplier (POSTING_PENDING) with its expected credit; 12C credits 300 L less and writes the rest off. ExpectedCredits on the invoice service lists them. TP is not seeded: expected credits are USD-only in the credit memo R1.</t>
         </is>
       </c>
     </row>
@@ -32905,7 +32905,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL - shows the gap</t>
+          <t>YES (B6) - expected credit; credit memo when that branch merges</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -32950,7 +32950,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Load the credit note as an invoice and Validate: INV456 HARD on the negative line (no field marks a defuel). Full demo needs document_type CREDIT_NOTE.</t>
+          <t>Defueling app: the defuel is posted to the supplier (POSTING_PENDING) with its expected credit; 12C credits 300 L less and writes the rest off. ExpectedCredits on the invoice service lists them. TP is not seeded: expected credits are USD-only in the credit memo R1.</t>
         </is>
       </c>
     </row>
@@ -32965,7 +32965,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>NO - needs schema (proposed sheets)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -33006,7 +33006,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Needs storage-location master and movement type. Data ready in PROPOSED_DEFUEL_TICKETS / PROPOSED_STORAGE_LOCATIONS.</t>
+          <t>Defueling app: the defuel moves the fuel into the station's TEMP tank; the stock valuation shows the batch leaving the tail and arriving in the tank at its own rate, and ROB falls by the same amount.</t>
         </is>
       </c>
     </row>
@@ -33021,7 +33021,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>NO - needs schema (proposed sheets)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Needs storage-location master and movement type. Data ready in PROPOSED_DEFUEL_TICKETS / PROPOSED_STORAGE_LOCATIONS.</t>
+          <t>Defueling app: the defuel moves the fuel into the station's TEMP tank; the stock valuation shows the batch leaving the tail and arriving in the tank at its own rate, and ROB falls by the same amount.</t>
         </is>
       </c>
     </row>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>NO - needs schema (proposed sheets)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -33118,7 +33118,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Needs storage-location master and movement type. Data ready in PROPOSED_DEFUEL_TICKETS / PROPOSED_STORAGE_LOCATIONS.</t>
+          <t>Defueling app: the defuel moves the fuel into the station's TEMP tank; the stock valuation shows the batch leaving the tail and arriving in the tank at its own rate, and ROB falls by the same amount.</t>
         </is>
       </c>
     </row>

--- a/docs/test-data/scenarios/JetBlue_B6_Scenario_Seed_2026-09-24_to_26.xlsx
+++ b/docs/test-data/scenarios/JetBlue_B6_Scenario_Seed_2026-09-24_to_26.xlsx
@@ -471,9 +471,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -509,9 +507,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -533,9 +529,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -564,9 +558,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -830,7 +822,6 @@
           <t>2026-10-27T00:00:00Z</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>b3426936-fb7a-59e0-adae-13e8ff46692f</t>
@@ -1073,10 +1064,6 @@
           <t>LOOKUP</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>3d5ad164-45a1-5207-a52e-d2b125e71c6a</t>
@@ -1112,10 +1099,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>true</t>
@@ -1183,10 +1166,6 @@
           <t>0.0380</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1217,10 +1196,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>true</t>
@@ -1288,10 +1263,6 @@
           <t>0.0160</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1322,10 +1293,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>true</t>
@@ -1393,10 +1360,6 @@
           <t>0.0090</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1427,10 +1390,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>true</t>
@@ -1595,7 +1554,6 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>true</t>
@@ -1663,7 +1621,6 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>true</t>
@@ -1731,7 +1688,6 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>true</t>
@@ -1799,7 +1755,6 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>true</t>
@@ -1867,7 +1822,6 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>true</t>
@@ -1935,7 +1889,6 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>true</t>
@@ -2003,7 +1956,6 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>true</t>
@@ -2071,7 +2023,6 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>true</t>
@@ -2139,7 +2090,6 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>true</t>
@@ -2207,7 +2157,6 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>true</t>
@@ -2275,7 +2224,6 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>true</t>
@@ -2642,7 +2590,6 @@
           <t>FO-JFK-20260926-M1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>cee706fa-bd55-5699-bb00-e0f071e69e6d</t>
@@ -2743,10 +2690,6 @@
           <t>SCENARIO 10 - maintenance uplift to tail N999JQ at JFK: Engine ground run after component change. No flight. Cost object: maintenance, not a flight.</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
           <t>ACKNOWLEDGED</t>
@@ -2762,7 +2705,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
           <t>2026-09-26T14:05:03Z</t>
@@ -2783,22 +2725,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr">
         <is>
           <t>ORIGINAL</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr">
         <is>
           <t>953e6b5c-2942-55fd-9354-1bf931d13584</t>
@@ -2831,7 +2762,6 @@
           <t>FO-JFK-20260925-M2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>cee706fa-bd55-5699-bb00-e0f071e69e6d</t>
@@ -2932,10 +2862,6 @@
           <t>SCENARIO 10 - maintenance uplift to tail N2044J at JFK: Fuel-system leak check after wing tank access. No flight. Cost object: maintenance, not a flight.</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
           <t>ACKNOWLEDGED</t>
@@ -2951,7 +2877,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
           <t>2026-09-25T20:19:25Z</t>
@@ -2972,22 +2897,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr">
         <is>
           <t>ORIGINAL</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="inlineStr">
         <is>
           <t>953e6b5c-2942-55fd-9354-1bf931d13584</t>
@@ -3020,7 +2934,6 @@
           <t>FO-JFK-20260926-M3</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>cee706fa-bd55-5699-bb00-e0f071e69e6d</t>
@@ -3121,10 +3034,6 @@
           <t>SCENARIO 10 - maintenance uplift to tail N651JB at JFK: Post-maintenance engine run-up before return to service. No flight. Cost object: maintenance, not a flight.</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
           <t>ACKNOWLEDGED</t>
@@ -3140,7 +3049,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
           <t>2026-09-26T14:18:30Z</t>
@@ -3161,22 +3069,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr">
         <is>
           <t>ORIGINAL</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr">
         <is>
           <t>953e6b5c-2942-55fd-9354-1bf931d13584</t>
@@ -3571,11 +3468,6 @@
           <t>3686.65</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -3586,7 +3478,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>NOT_ATTRIBUTABLE</t>
@@ -3612,7 +3503,6 @@
           <t>Fueler 777 (synthetic)</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MRO technician 312 (synthetic)</t>
@@ -3638,14 +3528,11 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
         <is>
           <t>2026-09-26T15:05:03Z</t>
@@ -3681,16 +3568,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr">
         <is>
           <t>NOT_ATTRIBUTABLE</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
           <t>B6</t>
@@ -3758,11 +3640,6 @@
           <t>3988.95</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -3773,7 +3650,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>NOT_ATTRIBUTABLE</t>
@@ -3799,7 +3675,6 @@
           <t>Fueler 777 (synthetic)</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MRO technician 312 (synthetic)</t>
@@ -3825,14 +3700,11 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>2026-09-25T21:19:25Z</t>
@@ -3868,16 +3740,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr">
         <is>
           <t>NOT_ATTRIBUTABLE</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
           <t>B6</t>
@@ -3945,11 +3812,6 @@
           <t>4205.16</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -3960,7 +3822,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>NOT_ATTRIBUTABLE</t>
@@ -3986,7 +3847,6 @@
           <t>Fueler 777 (synthetic)</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MRO technician 312 (synthetic)</t>
@@ -4012,14 +3872,11 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>2026-09-26T15:18:30Z</t>
@@ -4055,16 +3912,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr">
         <is>
           <t>NOT_ATTRIBUTABLE</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -4360,7 +4212,6 @@
           <t>SNL-AMS-485591</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>FT-AMS-20260924-0001-D</t>
@@ -4456,8 +4307,6 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>HD-AMS-06</t>
@@ -4550,7 +4399,6 @@
           <t>CGASEA788537</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>FT-SEA-20260923-0001-D</t>
@@ -4646,8 +4494,6 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>HD-SEA-18</t>
@@ -4740,7 +4586,6 @@
           <t>WFS-JFK-M2609261</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>FT-JFK-20260926-M1</t>
@@ -4756,7 +4601,6 @@
           <t>N999JQ</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>3683.00</t>
@@ -4812,7 +4656,6 @@
           <t>2950.08</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
           <t>2026-09-26T15:05:03Z</t>
@@ -4873,7 +4716,6 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr">
         <is>
           <t>1.2886</t>
@@ -4926,7 +4768,6 @@
           <t>WFS-JFK-M2609252</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>FT-JFK-20260925-M2</t>
@@ -4942,7 +4783,6 @@
           <t>N2044J</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>3985.00</t>
@@ -4998,7 +4838,6 @@
           <t>3191.99</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>2026-09-25T21:19:25Z</t>
@@ -5059,7 +4898,6 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr">
         <is>
           <t>1.2886</t>
@@ -5112,7 +4950,6 @@
           <t>WFS-JFK-M2609263</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>FT-JFK-20260926-M3</t>
@@ -5128,7 +4965,6 @@
           <t>N651JB</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>4201.00</t>
@@ -5184,7 +5020,6 @@
           <t>3365.00</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>2026-09-26T15:18:30Z</t>
@@ -5245,7 +5080,6 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr">
         <is>
           <t>1.2886</t>
@@ -5647,7 +5481,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -5698,16 +5531,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>APPROVED</t>
@@ -5738,14 +5566,11 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
           <t>VERIFIED</t>
@@ -5781,13 +5606,11 @@
           <t>SCENARIO 16 - original invoice, validated CLEAR and approved, POSTING PENDING: nothing has been posted to S/4.</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -5808,19 +5631,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="inlineStr">
         <is>
           <t>WITHIN</t>
@@ -5853,7 +5668,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -5904,16 +5718,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -5924,18 +5733,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -5946,7 +5748,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>0</t>
@@ -5967,13 +5768,11 @@
           <t>SCENARIO 16A - the supplier sent invoice 77004512 again three days later. Same number, same vendor, same lines.</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
           <t>2026-09-30T10:00:00Z</t>
@@ -5994,20 +5793,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6035,7 +5825,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -6086,16 +5875,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>APPROVED</t>
@@ -6126,14 +5910,11 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
           <t>VERIFIED</t>
@@ -6169,13 +5950,11 @@
           <t>SCENARIO 16 - original invoice, validated CLEAR and approved, POSTING PENDING: nothing has been posted to S/4.</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -6196,19 +5975,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr">
         <is>
           <t>WITHIN</t>
@@ -6241,7 +6012,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -6292,16 +6062,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -6312,18 +6077,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -6334,7 +6092,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>0</t>
@@ -6355,13 +6112,11 @@
           <t>SCENARIO 16B - the supplier re-issued 77004513 under a NEW number 77004513-R, billing the same tickets.</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
           <t>2026-10-02T10:00:00Z</t>
@@ -6382,20 +6137,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6423,7 +6169,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -6474,16 +6219,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -6494,18 +6234,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -6516,7 +6249,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>0</t>
@@ -6537,13 +6269,11 @@
           <t>SCENARIO 16C - CONTROL. Another vendor happens to use invoice number 77004512.</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -6564,20 +6294,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6605,7 +6326,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -6656,16 +6376,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -6676,18 +6391,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -6698,7 +6406,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>0</t>
@@ -6719,13 +6426,11 @@
           <t>SCENARIO 2 - price mismatch. Line 10 billed at 1.2706 against the order price 1.2630 (+0.6%). Line 20 is correct. Not validated: press Validate.</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -6746,20 +6451,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6787,7 +6483,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -6838,16 +6533,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -6858,18 +6548,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -6880,7 +6563,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>0</t>
@@ -6901,13 +6583,11 @@
           <t>SCENARIO 2 - price mismatch. Line 10 billed at 1.2428 against the order price 1.2208 (+1.8%). Line 20 is correct. Not validated: press Validate.</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -6928,20 +6608,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6969,7 +6640,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -7020,16 +6690,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -7040,18 +6705,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -7062,7 +6720,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>0</t>
@@ -7083,13 +6740,11 @@
           <t>SCENARIO 2 - price mismatch. Line 10 billed at 1.3582 against the order price 1.2997 (+4.5%). Line 20 is correct. Not validated: press Validate.</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -7110,20 +6765,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7151,7 +6797,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -7202,16 +6847,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -7222,18 +6862,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -7244,7 +6877,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr">
         <is>
           <t>0</t>
@@ -7265,13 +6897,11 @@
           <t>SCENARIO 3 - price components. The order is on contract B6-WFS-2026-CMP, whose formula FRM-B6-CMP prices Platts USGC, Supplier Differential, Into-Plane Fee, Airport Throughput Fee. Run Derive Price on the contract first, then Validate.</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -7292,20 +6922,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7333,7 +6954,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -7384,16 +7004,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -7404,18 +7019,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -7426,7 +7034,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>0</t>
@@ -7447,13 +7054,11 @@
           <t>SCENARIO 3 - price components. The order is on contract B6-WFS-2026-CMP, whose formula FRM-B6-CMP prices Platts USGC, Supplier Differential, Into-Plane Fee, Airport Throughput Fee. Run Derive Price on the contract first, then Validate.</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -7474,20 +7079,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7515,7 +7111,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -7566,16 +7161,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -7586,18 +7176,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -7608,7 +7191,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>0</t>
@@ -7629,13 +7211,11 @@
           <t>SCENARIO 3 - price components. The order is on contract B6-WFS-2026-CMP, whose formula FRM-B6-CMP prices Platts USGC, Supplier Differential, Into-Plane Fee, Airport Throughput Fee. Run Derive Price on the contract first, then Validate.</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -7656,20 +7236,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7697,7 +7268,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -7748,16 +7318,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -7768,18 +7333,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -7790,7 +7348,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>0</t>
@@ -7811,13 +7368,11 @@
           <t>SCENARIO 4 - quantity mismatch. Line 10 bills 20057.000 L against the ticket and goods receipt of 20362.000 L (-1.5%). Line 20 is correct. Press Validate.</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -7838,20 +7393,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7879,7 +7425,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -7930,16 +7475,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -7950,18 +7490,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -7972,7 +7505,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr">
         <is>
           <t>0</t>
@@ -7993,13 +7525,11 @@
           <t>SCENARIO 4 - quantity mismatch. Line 10 bills 9232.000 L against the ticket and goods receipt of 9567.000 L (-3.5%). Line 20 is correct. Press Validate.</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -8020,20 +7550,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8061,7 +7582,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -8112,16 +7632,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -8132,18 +7647,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -8154,7 +7662,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr">
         <is>
           <t>0</t>
@@ -8175,13 +7682,11 @@
           <t>SCENARIO 4 - quantity mismatch. Line 10 bills 4274.000 L against the ticket and goods receipt of 4032.000 L (+6.0%). Line 20 is correct. Press Validate.</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -8202,20 +7707,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8243,7 +7739,6 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -8294,16 +7789,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -8314,18 +7804,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -8336,7 +7819,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr">
         <is>
           <t>0</t>
@@ -8357,13 +7839,11 @@
           <t>SCENARIO 7 - uplifts flown on 2026-09-26 and captured on 2026-10-02, after the 2026-09 close. Invoiced late.</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -8384,20 +7864,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8425,7 +7896,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -8476,16 +7946,11 @@
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -8496,18 +7961,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -8518,7 +7976,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr">
         <is>
           <t>0</t>
@@ -8539,13 +7996,11 @@
           <t>SCENARIO 10 - maintenance uplifts to tails with no flight.</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
           <t>2026-09-27T15:00:00Z</t>
@@ -8566,20 +8021,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8889,9 +8335,6 @@
           <t>d43b0051-93ba-59ac-80a4-5181ea56a22e</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>FUELLGA</t>
@@ -8907,8 +8350,6 @@
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -8919,11 +8360,6 @@
           <t>78456c96-f3de-5fd2-b161-7eb8f1c41483</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
           <t>FUEL</t>
@@ -9021,9 +8457,6 @@
           <t>f2cb8cae-e9e0-5f7a-b60c-9c2b0d18635b</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>FUELLGA</t>
@@ -9039,8 +8472,6 @@
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -9051,11 +8482,6 @@
           <t>31cd5aab-e947-57dd-acd9-a0a20cf095d3</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
           <t>FUEL</t>
@@ -9153,9 +8579,6 @@
           <t>ea4a4ac5-c928-5ed4-9a90-11e61214d3da</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>FUELJFK</t>
@@ -9171,8 +8594,6 @@
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -9183,11 +8604,6 @@
           <t>7cc7376c-c7c8-56a5-ac56-3e20be3d703d</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
           <t>FUEL</t>
@@ -9285,9 +8701,6 @@
           <t>943f9872-df9a-5bd8-b681-9aa857e9a5cb</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>FUELJFK</t>
@@ -9303,8 +8716,6 @@
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -9315,11 +8726,6 @@
           <t>87d59fd2-d3a3-540f-a636-a95205d940aa</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
           <t>FUEL</t>
@@ -9417,9 +8823,6 @@
           <t>22ef5e98-4620-52a1-a06f-4f3330396716</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>MROJFK</t>
@@ -9435,19 +8838,11 @@
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
           <t>FUEL</t>
@@ -9545,9 +8940,6 @@
           <t>ea4b9060-4fbc-50a4-9088-22f36c9527a7</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>MROJFK</t>
@@ -9563,19 +8955,11 @@
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
           <t>FUEL</t>
@@ -9673,9 +9057,6 @@
           <t>619b54e6-7a6d-5da2-9270-ddcf70e9a291</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>MROJFK</t>
@@ -9691,19 +9072,11 @@
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr">
         <is>
           <t>FUEL</t>
@@ -10115,7 +9488,6 @@
           <t>22623d49-4a07-5401-afd7-918b60f77bc7</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10335,7 +9707,6 @@
           <t>bf38e393-c188-5663-88c1-0fb09859f4da</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10363,7 +9734,6 @@
           <t>8999f243-3daf-5932-8631-f2ff6a4be1b6</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10615,7 +9985,6 @@
           <t>670a3193-b5a7-58d8-be21-19e59ae44e8d</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11091,7 +10460,6 @@
           <t>4545b7cc-f827-541c-a2e5-d65424e6781b</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -11311,7 +10679,6 @@
           <t>93fffd08-b9f5-53c4-8684-e5320b2a3cd2</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -11659,7 +11026,6 @@
           <t>22623d49-4a07-5401-afd7-918b60f77bc7</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -11719,7 +11085,6 @@
           <t>B61236</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -11811,7 +11176,6 @@
           <t>fuel.ops@airline.com</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -11839,7 +11203,6 @@
           <t>2026-09-24T13:12:06Z</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -11931,7 +11294,6 @@
           <t>bf38e393-c188-5663-88c1-0fb09859f4da</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -11959,7 +11321,6 @@
           <t>8999f243-3daf-5932-8631-f2ff6a4be1b6</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -12019,7 +11380,6 @@
           <t>B62954</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -12111,7 +11471,6 @@
           <t>fuel.ops@airline.com</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -12139,7 +11498,6 @@
           <t>2026-09-26T04:49:57Z</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -12231,7 +11589,6 @@
           <t>670a3193-b5a7-58d8-be21-19e59ae44e8d</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -12387,7 +11744,6 @@
           <t>efb22aaf-5511-5806-bab2-615c6a858452</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -12543,7 +11899,6 @@
           <t>3070ea52-2dad-51d2-954e-7be83eac7c68</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -12667,7 +12022,6 @@
           <t>4545b7cc-f827-541c-a2e5-d65424e6781b</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -12727,7 +12081,6 @@
           <t>B6434</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -12819,7 +12172,6 @@
           <t>fuel.ops@airline.com</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12847,7 +12199,6 @@
           <t>2026-09-26T16:32:36Z</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12939,7 +12290,6 @@
           <t>93fffd08-b9f5-53c4-8684-e5320b2a3cd2</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -13095,7 +12445,6 @@
           <t>33cde6e9-9793-5cd9-b27e-d89b5999a637</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -13539,7 +12888,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -13567,7 +12915,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -13595,7 +12942,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -13655,7 +13001,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -13683,7 +13028,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -13711,7 +13055,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13739,7 +13082,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -13831,7 +13173,6 @@
           <t>2026-10-13T16:02:21Z</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13859,7 +13200,6 @@
           <t>397</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13887,7 +13227,6 @@
           <t>327</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13915,7 +13254,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -13943,7 +13281,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13971,7 +13308,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13999,7 +13335,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14219,7 +13554,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14247,7 +13581,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -14275,7 +13608,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -14335,7 +13667,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -14363,7 +13694,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -14391,7 +13721,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -14419,7 +13748,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14511,7 +13839,6 @@
           <t>2026-10-13T16:02:08Z</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14539,7 +13866,6 @@
           <t>108</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -14567,7 +13893,6 @@
           <t>89</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -14595,7 +13920,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -14623,7 +13947,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14651,7 +13974,6 @@
           <t>19</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -14679,7 +14001,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -14739,7 +14060,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -14767,7 +14087,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -14795,7 +14114,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -14855,7 +14173,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -14883,7 +14200,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -14911,7 +14227,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -14939,7 +14254,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -15031,7 +14345,6 @@
           <t>2026-10-13T16:02:09Z</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -15059,7 +14372,6 @@
           <t>737</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -15087,7 +14399,6 @@
           <t>607</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -15115,7 +14426,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -15143,7 +14453,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -15171,7 +14480,6 @@
           <t>130</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -15199,7 +14507,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -15259,7 +14566,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -15287,7 +14593,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -15315,7 +14620,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -15375,7 +14679,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -15403,7 +14706,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -15431,7 +14733,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -15459,7 +14760,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -15551,7 +14851,6 @@
           <t>2026-10-13T16:02:09Z</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -15579,7 +14878,6 @@
           <t>363</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -15607,7 +14905,6 @@
           <t>299</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -15635,7 +14932,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -15663,7 +14959,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -15691,7 +14986,6 @@
           <t>64</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -15719,7 +15013,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -15939,7 +15232,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -15967,7 +15259,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -15995,7 +15286,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -16055,7 +15345,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -16083,7 +15372,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -16111,7 +15399,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -16139,7 +15426,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -16231,7 +15517,6 @@
           <t>2026-10-13T16:02:11Z</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -16259,7 +15544,6 @@
           <t>74</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -16287,7 +15571,6 @@
           <t>61</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -16315,7 +15598,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -16343,7 +15625,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -16371,7 +15652,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -16399,7 +15679,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -16651,7 +15930,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -16679,7 +15957,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -16707,7 +15984,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -16767,7 +16043,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -16795,7 +16070,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -16823,7 +16097,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -16851,7 +16124,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -16943,7 +16215,6 @@
           <t>2026-10-13T16:02:22Z</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -16971,7 +16242,6 @@
           <t>312</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -16999,7 +16269,6 @@
           <t>257</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -17027,7 +16296,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -17055,7 +16323,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -17083,7 +16350,6 @@
           <t>55</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -17111,7 +16377,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -17363,7 +16628,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -17391,7 +16655,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -17419,7 +16682,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -17479,7 +16741,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -17507,7 +16768,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -17535,7 +16795,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -17563,7 +16822,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -17655,7 +16913,6 @@
           <t>2026-10-13T16:02:23Z</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -17683,7 +16940,6 @@
           <t>1145</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -17711,7 +16967,6 @@
           <t>943</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -17739,7 +16994,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -17767,7 +17021,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -17795,7 +17048,6 @@
           <t>202</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -17823,7 +17075,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -18075,7 +17326,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -18103,7 +17353,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -18131,7 +17380,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -18191,7 +17439,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -18219,7 +17466,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -18247,7 +17493,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -18275,7 +17520,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -18367,7 +17611,6 @@
           <t>2026-10-13T16:02:23Z</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -18395,7 +17638,6 @@
           <t>142</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -18423,7 +17665,6 @@
           <t>117</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -18451,7 +17692,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -18479,7 +17719,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -18507,7 +17746,6 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -18535,7 +17773,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -18787,7 +18024,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -18815,7 +18051,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -18843,7 +18078,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -18903,7 +18137,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -18931,7 +18164,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -18959,7 +18191,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -18987,7 +18218,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -19079,7 +18309,6 @@
           <t>2026-10-13T16:02:20Z</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -19107,7 +18336,6 @@
           <t>1842</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -19135,7 +18363,6 @@
           <t>1517</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -19163,7 +18390,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -19191,7 +18417,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -19219,7 +18444,6 @@
           <t>325</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -19247,7 +18471,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -19499,7 +18722,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -19527,7 +18749,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -19555,7 +18776,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -19615,7 +18835,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -19643,7 +18862,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -19671,7 +18889,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -19699,7 +18916,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -19791,7 +19007,6 @@
           <t>2026-10-13T16:02:24Z</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -19819,7 +19034,6 @@
           <t>567</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -19847,7 +19061,6 @@
           <t>467</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -19875,7 +19088,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -19903,7 +19115,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -19931,7 +19142,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -19959,7 +19169,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -20019,7 +19228,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -20047,7 +19255,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -20075,7 +19282,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -20135,7 +19341,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -20163,7 +19368,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -20191,7 +19395,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -20219,7 +19422,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -20311,7 +19513,6 @@
           <t>2026-10-13T16:02:10Z</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -20339,7 +19540,6 @@
           <t>1145</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -20367,7 +19567,6 @@
           <t>943</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -20395,7 +19594,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -20423,7 +19621,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -20451,7 +19648,6 @@
           <t>202</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -20479,7 +19675,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -20731,7 +19926,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -20759,7 +19953,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -20787,7 +19980,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -20847,7 +20039,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -20875,7 +20066,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -20903,7 +20093,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -20931,7 +20120,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -21023,7 +20211,6 @@
           <t>2026-10-13T16:02:11Z</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -21051,7 +20238,6 @@
           <t>261</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -21079,7 +20265,6 @@
           <t>215</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -21107,7 +20292,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -21135,7 +20319,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -21163,7 +20346,6 @@
           <t>46</t>
         </is>
       </c>
-      <c r="F381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -21191,7 +20373,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -21251,7 +20432,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -21279,7 +20459,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -21307,7 +20486,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -21367,7 +20545,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -21395,7 +20572,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -21423,7 +20599,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -21451,7 +20626,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -21543,7 +20717,6 @@
           <t>2026-10-13T16:02:12Z</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -21571,7 +20744,6 @@
           <t>584</t>
         </is>
       </c>
-      <c r="F395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -21599,7 +20771,6 @@
           <t>481</t>
         </is>
       </c>
-      <c r="F396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -21627,7 +20798,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -21655,7 +20825,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -21683,7 +20852,6 @@
           <t>103</t>
         </is>
       </c>
-      <c r="F399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -21711,7 +20879,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -21771,7 +20938,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -21799,7 +20965,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -21827,7 +20992,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -21887,7 +21051,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -21915,7 +21078,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -21943,7 +21105,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -21971,7 +21132,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -22063,7 +21223,6 @@
           <t>2026-10-13T16:02:18Z</t>
         </is>
       </c>
-      <c r="F412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -22091,7 +21250,6 @@
           <t>873</t>
         </is>
       </c>
-      <c r="F413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -22119,7 +21277,6 @@
           <t>719</t>
         </is>
       </c>
-      <c r="F414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -22147,7 +21304,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -22175,7 +21331,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -22203,7 +21358,6 @@
           <t>154</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -22231,7 +21385,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -22483,7 +21636,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -22511,7 +21663,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -22539,7 +21690,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -22599,7 +21749,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -22627,7 +21776,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -22655,7 +21803,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -22683,7 +21830,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -22775,7 +21921,6 @@
           <t>2026-10-13T16:02:13Z</t>
         </is>
       </c>
-      <c r="F436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -22803,7 +21948,6 @@
           <t>74</t>
         </is>
       </c>
-      <c r="F437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -22831,7 +21975,6 @@
           <t>61</t>
         </is>
       </c>
-      <c r="F438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -22859,7 +22002,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -22887,7 +22029,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -22915,7 +22056,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="F441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -22943,7 +22083,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -23195,7 +22334,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -23223,7 +22361,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -23251,7 +22388,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -23311,7 +22447,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -23339,7 +22474,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -23367,7 +22501,6 @@
           <t>SYSTEM (auto-approved: three-way matched within tolerance)</t>
         </is>
       </c>
-      <c r="F456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -23395,7 +22528,6 @@
           <t>2026-09-27T16:00:00Z</t>
         </is>
       </c>
-      <c r="F457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -23487,7 +22619,6 @@
           <t>2026-10-13T16:02:11Z</t>
         </is>
       </c>
-      <c r="F460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -23515,7 +22646,6 @@
           <t>448</t>
         </is>
       </c>
-      <c r="F461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -23543,7 +22673,6 @@
           <t>369</t>
         </is>
       </c>
-      <c r="F462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -23571,7 +22700,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -23599,7 +22727,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -23627,7 +22754,6 @@
           <t>79</t>
         </is>
       </c>
-      <c r="F465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -23655,7 +22781,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -24035,7 +23160,6 @@
           <t>4500300105</t>
         </is>
       </c>
-      <c r="F478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -24063,7 +23187,6 @@
           <t>5000300105</t>
         </is>
       </c>
-      <c r="F479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -24091,7 +23214,6 @@
           <t>TICKET_NUMBER</t>
         </is>
       </c>
-      <c r="F480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -24151,7 +23273,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -24179,7 +23300,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -24207,7 +23327,6 @@
           <t>16471.82</t>
         </is>
       </c>
-      <c r="F484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -24235,7 +23354,6 @@
           <t>1.5548</t>
         </is>
       </c>
-      <c r="F485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -24263,7 +23381,6 @@
           <t>25611.11</t>
         </is>
       </c>
-      <c r="F486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -24291,7 +23408,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -24351,7 +23467,6 @@
           <t>4500300135</t>
         </is>
       </c>
-      <c r="F489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -24379,7 +23494,6 @@
           <t>5000300135</t>
         </is>
       </c>
-      <c r="F490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -24407,7 +23521,6 @@
           <t>TICKET_NUMBER</t>
         </is>
       </c>
-      <c r="F491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -24467,7 +23580,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -24495,7 +23607,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -24523,7 +23634,6 @@
           <t>19525.98</t>
         </is>
       </c>
-      <c r="F495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -24551,7 +23661,6 @@
           <t>1.5606</t>
         </is>
       </c>
-      <c r="F496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -24579,7 +23688,6 @@
           <t>30472.4</t>
         </is>
       </c>
-      <c r="F497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -24607,7 +23715,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -24635,7 +23742,6 @@
           <t>8999f243-3daf-5932-8631-f2ff6a4be1b6</t>
         </is>
       </c>
-      <c r="F499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -24663,7 +23769,6 @@
           <t>670a3193-b5a7-58d8-be21-19e59ae44e8d</t>
         </is>
       </c>
-      <c r="F500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -24691,7 +23796,6 @@
           <t>22623d49-4a07-5401-afd7-918b60f77bc7</t>
         </is>
       </c>
-      <c r="F501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -24719,7 +23823,6 @@
           <t>bf38e393-c188-5663-88c1-0fb09859f4da</t>
         </is>
       </c>
-      <c r="F502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -24843,7 +23946,6 @@
           <t>4500300136</t>
         </is>
       </c>
-      <c r="F506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -24871,7 +23973,6 @@
           <t>5000300136</t>
         </is>
       </c>
-      <c r="F507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -24899,7 +24000,6 @@
           <t>TICKET_NUMBER</t>
         </is>
       </c>
-      <c r="F508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -24959,7 +24059,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -24987,7 +24086,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -25015,7 +24113,6 @@
           <t>16342.54</t>
         </is>
       </c>
-      <c r="F512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -25043,7 +24140,6 @@
           <t>1.6044</t>
         </is>
       </c>
-      <c r="F513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -25071,7 +24167,6 @@
           <t>26220.15</t>
         </is>
       </c>
-      <c r="F514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -25099,7 +24194,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -25159,7 +24253,6 @@
           <t>4500300756</t>
         </is>
       </c>
-      <c r="F517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -25187,7 +24280,6 @@
           <t>5000300756</t>
         </is>
       </c>
-      <c r="F518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -25215,7 +24307,6 @@
           <t>TICKET_NUMBER</t>
         </is>
       </c>
-      <c r="F519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -25275,7 +24366,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -25303,7 +24393,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -25331,7 +24420,6 @@
           <t>14379.96</t>
         </is>
       </c>
-      <c r="F523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -25359,7 +24447,6 @@
           <t>1.5963</t>
         </is>
       </c>
-      <c r="F524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -25387,7 +24474,6 @@
           <t>22955.24</t>
         </is>
       </c>
-      <c r="F525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -25415,7 +24501,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -25571,7 +24656,6 @@
           <t>4500300141</t>
         </is>
       </c>
-      <c r="F531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -25599,7 +24683,6 @@
           <t>5000300141</t>
         </is>
       </c>
-      <c r="F532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -25627,7 +24710,6 @@
           <t>TICKET_NUMBER</t>
         </is>
       </c>
-      <c r="F533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -25687,7 +24769,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -25715,7 +24796,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -25743,7 +24823,6 @@
           <t>6130.24</t>
         </is>
       </c>
-      <c r="F537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -25771,7 +24850,6 @@
           <t>1.6287</t>
         </is>
       </c>
-      <c r="F538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -25799,7 +24877,6 @@
           <t>9984.3</t>
         </is>
       </c>
-      <c r="F539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -25827,7 +24904,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -25887,7 +24963,6 @@
           <t>4500300160</t>
         </is>
       </c>
-      <c r="F542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -25915,7 +24990,6 @@
           <t>5000300160</t>
         </is>
       </c>
-      <c r="F543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -25943,7 +25017,6 @@
           <t>TICKET_NUMBER</t>
         </is>
       </c>
-      <c r="F544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -26003,7 +25076,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -26031,7 +25103,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -26059,7 +25130,6 @@
           <t>14880.05</t>
         </is>
       </c>
-      <c r="F548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -26087,7 +25157,6 @@
           <t>1.6271</t>
         </is>
       </c>
-      <c r="F549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -26115,7 +25184,6 @@
           <t>24210.81</t>
         </is>
       </c>
-      <c r="F550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -26143,7 +25211,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -26299,7 +25366,6 @@
           <t>4500300013</t>
         </is>
       </c>
-      <c r="F556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -26327,7 +25393,6 @@
           <t>5000300013</t>
         </is>
       </c>
-      <c r="F557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -26355,7 +25420,6 @@
           <t>TICKET_NUMBER</t>
         </is>
       </c>
-      <c r="F558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -26415,7 +25479,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -26443,7 +25506,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -26471,7 +25533,6 @@
           <t>3201.41</t>
         </is>
       </c>
-      <c r="F562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -26499,7 +25560,6 @@
           <t>1.5413</t>
         </is>
       </c>
-      <c r="F563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -26527,7 +25587,6 @@
           <t>4934.36</t>
         </is>
       </c>
-      <c r="F564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -26555,7 +25614,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -26615,7 +25673,6 @@
           <t>4500300015</t>
         </is>
       </c>
-      <c r="F567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -26643,7 +25700,6 @@
           <t>5000300015</t>
         </is>
       </c>
-      <c r="F568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -26671,7 +25727,6 @@
           <t>TICKET_NUMBER</t>
         </is>
       </c>
-      <c r="F569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -26731,7 +25786,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -26759,7 +25813,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -26787,7 +25840,6 @@
           <t>6124.38</t>
         </is>
       </c>
-      <c r="F573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -26815,7 +25867,6 @@
           <t>1.5436</t>
         </is>
       </c>
-      <c r="F574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -26843,7 +25894,6 @@
           <t>9453.85</t>
         </is>
       </c>
-      <c r="F575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -26871,7 +25921,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -27219,7 +26268,6 @@
           <t>efb22aaf-5511-5806-bab2-615c6a858452</t>
         </is>
       </c>
-      <c r="F587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -27311,7 +26359,6 @@
           <t>4545b7cc-f827-541c-a2e5-d65424e6781b</t>
         </is>
       </c>
-      <c r="F590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -27339,7 +26386,6 @@
           <t>93fffd08-b9f5-53c4-8684-e5320b2a3cd2</t>
         </is>
       </c>
-      <c r="F591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -27367,7 +26413,6 @@
           <t>3070ea52-2dad-51d2-954e-7be83eac7c68</t>
         </is>
       </c>
-      <c r="F592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -27395,7 +26440,6 @@
           <t>33cde6e9-9793-5cd9-b27e-d89b5999a637</t>
         </is>
       </c>
-      <c r="F593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -27551,7 +26595,6 @@
           <t>4500300090</t>
         </is>
       </c>
-      <c r="F598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -27579,7 +26622,6 @@
           <t>5000300090</t>
         </is>
       </c>
-      <c r="F599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -27607,7 +26649,6 @@
           <t>TICKET_NUMBER</t>
         </is>
       </c>
-      <c r="F600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -27667,7 +26708,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -27695,7 +26735,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -27723,7 +26762,6 @@
           <t>7665.08</t>
         </is>
       </c>
-      <c r="F604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -27751,7 +26789,6 @@
           <t>1.5819</t>
         </is>
       </c>
-      <c r="F605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -27779,7 +26816,6 @@
           <t>12125.22</t>
         </is>
       </c>
-      <c r="F606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -27807,7 +26843,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -27867,7 +26902,6 @@
           <t>4500300733</t>
         </is>
       </c>
-      <c r="F609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -27895,7 +26929,6 @@
           <t>5000300733</t>
         </is>
       </c>
-      <c r="F610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -27923,7 +26956,6 @@
           <t>TICKET_NUMBER</t>
         </is>
       </c>
-      <c r="F611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -27983,7 +27015,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -28011,7 +27042,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -28039,7 +27069,6 @@
           <t>9131.5</t>
         </is>
       </c>
-      <c r="F615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -28067,7 +27096,6 @@
           <t>1.5996</t>
         </is>
       </c>
-      <c r="F616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -28095,7 +27123,6 @@
           <t>14606.54</t>
         </is>
       </c>
-      <c r="F617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -28123,7 +27150,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -28279,7 +27305,6 @@
           <t>4500300151</t>
         </is>
       </c>
-      <c r="F623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -28307,7 +27332,6 @@
           <t>5000300151</t>
         </is>
       </c>
-      <c r="F624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -28335,7 +27359,6 @@
           <t>TICKET_NUMBER</t>
         </is>
       </c>
-      <c r="F625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -28395,7 +27418,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -28423,7 +27445,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -28451,7 +27472,6 @@
           <t>7175.88</t>
         </is>
       </c>
-      <c r="F629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -28479,7 +27499,6 @@
           <t>1.5197</t>
         </is>
       </c>
-      <c r="F630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -28507,7 +27526,6 @@
           <t>10905.41</t>
         </is>
       </c>
-      <c r="F631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -28535,7 +27553,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -28595,7 +27612,6 @@
           <t>4500300182</t>
         </is>
       </c>
-      <c r="F634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -28623,7 +27639,6 @@
           <t>5000300182</t>
         </is>
       </c>
-      <c r="F635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -28651,7 +27666,6 @@
           <t>TICKET_NUMBER</t>
         </is>
       </c>
-      <c r="F636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -28711,7 +27725,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -28739,7 +27752,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -28767,7 +27779,6 @@
           <t>4567.71</t>
         </is>
       </c>
-      <c r="F640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -28795,7 +27806,6 @@
           <t>1.5173</t>
         </is>
       </c>
-      <c r="F641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -28823,7 +27833,6 @@
           <t>6930.48</t>
         </is>
       </c>
-      <c r="F642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -28851,7 +27860,6 @@
           <t>WITHIN</t>
         </is>
       </c>
-      <c r="F643" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29235,14 +28243,11 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>0.7979</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>18146.25</t>
@@ -29258,20 +28263,16 @@
           <t>-1835.17</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>CREW_REPORTED</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>NOT_RECONCILED</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -29282,21 +28283,11 @@
           <t>TRK-BOS-DF</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
         <is>
           <t>2026-09-24T02:40:57Z</t>
@@ -29337,12 +28328,6 @@
           <t>e9df6fac-e125-58d3-a1b0-7e62a04a4ec5</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -29353,7 +28338,6 @@
           <t>SUPPLIER_SERVICE</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr">
         <is>
           <t>Payload increase after fuelling put the aircraft over MTOW; supplier defuelled the excess</t>
@@ -29406,14 +28390,11 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>0.8063</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>9653.89</t>
@@ -29429,20 +28410,16 @@
           <t>-2311.66</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>CREW_REPORTED</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>NOT_RECONCILED</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -29453,21 +28430,11 @@
           <t>TRK-HPN-DF</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>2026-09-24T11:12:06Z</t>
@@ -29508,12 +28475,6 @@
           <t>e458f91c-819f-5c08-b46d-e2574369cf9d</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -29524,7 +28485,6 @@
           <t>SUPPLIER_SERVICE</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr">
         <is>
           <t>Aircraft change after fuelling (tail swap); fuel taken off the original tail by the supplier</t>
@@ -29577,14 +28537,11 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>0.7966</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>9096.73</t>
@@ -29600,20 +28557,16 @@
           <t>-2671.80</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>CREW_REPORTED</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>NOT_RECONCILED</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -29624,21 +28577,11 @@
           <t>TRK-BNA-DF</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>2026-09-25T00:44:46Z</t>
@@ -29679,12 +28622,6 @@
           <t>f429a01a-3138-5f1a-9dc6-0536e0f09046</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -29695,7 +28632,6 @@
           <t>SUPPLIER_SERVICE</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr">
         <is>
           <t>Fuel quality hold - supplier defuelled for sampling, service charged</t>
@@ -29748,14 +28684,11 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>0.8035</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>18491.07</t>
@@ -29771,20 +28704,16 @@
           <t>-2032.86</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>CREW_REPORTED</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>NOT_RECONCILED</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -29795,21 +28724,11 @@
           <t>TRK-SFO-DF</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>2026-09-25T06:55:23Z</t>
@@ -29850,12 +28769,6 @@
           <t>2902565d-8b21-566c-b1c9-0b443c03daf2</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -29866,7 +28779,6 @@
           <t>RETURN_TO_SUPPLIER</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr">
         <is>
           <t>Flight cancelled after fuelling; fuel returned to the supplier, credit note expected</t>
@@ -29919,14 +28831,11 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>0.7992</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>8448.61</t>
@@ -29942,20 +28851,16 @@
           <t>-1720.68</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>CREW_REPORTED</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>NOT_RECONCILED</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -29966,21 +28871,11 @@
           <t>TRK-BDL-DF</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>2026-09-25T14:22:36Z</t>
@@ -30021,12 +28916,6 @@
           <t>3c1b763a-5003-5d98-aa1f-47b7140020e5</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -30037,7 +28926,6 @@
           <t>RETURN_TO_SUPPLIER</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr">
         <is>
           <t>Over-fuelled by the supplier against the order; excess returned for credit</t>
@@ -30090,14 +28978,11 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>0.8056</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>20364.77</t>
@@ -30113,20 +28998,16 @@
           <t>-1665.98</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>CREW_REPORTED</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>NOT_RECONCILED</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -30137,21 +29018,11 @@
           <t>TRK-BOS-DF</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>2026-09-24T10:01:28Z</t>
@@ -30192,12 +29063,6 @@
           <t>3abb4049-23b6-592e-bd4d-d982f98eea18</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -30208,7 +29073,6 @@
           <t>RETURN_TO_SUPPLIER</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr">
         <is>
           <t>Contamination suspected; fuel returned, part credited and part disposed (write-off)</t>
@@ -30261,14 +29125,11 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>0.8095</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>19730.82</t>
@@ -30284,20 +29145,16 @@
           <t>-1905.56</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>CREW_REPORTED</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>NOT_RECONCILED</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -30308,21 +29165,11 @@
           <t>TRK-BOS-DF</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>2026-09-26T13:57:34Z</t>
@@ -30363,12 +29210,6 @@
           <t>ae487f03-9790-58e2-b22f-a860686866cd</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -30436,14 +29277,11 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>0.8081</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>17522.63</t>
@@ -30459,20 +29297,16 @@
           <t>-2738.65</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>CREW_REPORTED</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>NOT_RECONCILED</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -30483,21 +29317,11 @@
           <t>TRK-BOS-DF</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>2026-09-25T11:11:11Z</t>
@@ -30538,12 +29362,6 @@
           <t>da815508-f508-5d2a-9929-52abccfcfe3e</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -30611,14 +29429,11 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>0.8111</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>20427.02</t>
@@ -30634,20 +29449,16 @@
           <t>-3104.89</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>CREW_REPORTED</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>NOT_RECONCILED</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -30658,21 +29469,11 @@
           <t>TRK-LHR-DF</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr">
         <is>
           <t>2026-09-24T07:22:17Z</t>
@@ -30713,12 +29514,6 @@
           <t>f6511a80-8b79-5c65-818b-97b0cfca1523</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -32785,7 +31580,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>YES (B6) - expected credit; credit memo when that branch merges</t>
+          <t>YES (B6) - expected credit and its credit note</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -32830,7 +31625,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Defueling app: the defuel is posted to the supplier (POSTING_PENDING) with its expected credit; 12C credits 300 L less and writes the rest off. ExpectedCredits on the invoice service lists them. TP is not seeded: expected credits are USD-only in the credit memo R1.</t>
+          <t>Defueling app: the defuel is posted to the supplier (POSTING_PENDING) with its expected credit; 12C credits 300 L less and writes the rest off. ExpectedCredits lists them. Credit memo app: the supplier's credit note is seeded DRAFT against each expected credit - Post it and the expected credit clears (tools/seed-credit-memo-scenarios.js). TP is not seeded: expected credits are USD-only in the credit memo R1.</t>
         </is>
       </c>
     </row>
@@ -32845,7 +31640,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>YES (B6) - expected credit; credit memo when that branch merges</t>
+          <t>YES (B6) - expected credit and its credit note</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -32890,7 +31685,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Defueling app: the defuel is posted to the supplier (POSTING_PENDING) with its expected credit; 12C credits 300 L less and writes the rest off. ExpectedCredits on the invoice service lists them. TP is not seeded: expected credits are USD-only in the credit memo R1.</t>
+          <t>Defueling app: the defuel is posted to the supplier (POSTING_PENDING) with its expected credit; 12C credits 300 L less and writes the rest off. ExpectedCredits lists them. Credit memo app: the supplier's credit note is seeded DRAFT against each expected credit - Post it and the expected credit clears (tools/seed-credit-memo-scenarios.js). TP is not seeded: expected credits are USD-only in the credit memo R1.</t>
         </is>
       </c>
     </row>
@@ -32905,7 +31700,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>YES (B6) - expected credit; credit memo when that branch merges</t>
+          <t>YES (B6) - expected credit and its credit note</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -32950,7 +31745,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Defueling app: the defuel is posted to the supplier (POSTING_PENDING) with its expected credit; 12C credits 300 L less and writes the rest off. ExpectedCredits on the invoice service lists them. TP is not seeded: expected credits are USD-only in the credit memo R1.</t>
+          <t>Defueling app: the defuel is posted to the supplier (POSTING_PENDING) with its expected credit; 12C credits 300 L less and writes the rest off. ExpectedCredits lists them. Credit memo app: the supplier's credit note is seeded DRAFT against each expected credit - Post it and the expected credit clears (tools/seed-credit-memo-scenarios.js). TP is not seeded: expected credits are USD-only in the credit memo R1.</t>
         </is>
       </c>
     </row>
@@ -34141,7 +32936,6 @@
           <t>DF-SHL-BOS-26092411A</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>FT-BOS-20260924-DF11A</t>
@@ -34172,9 +32966,6 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
           <t>0.7979</t>
@@ -34190,7 +32981,6 @@
           <t>MEA</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>GR</t>
@@ -34201,22 +32991,16 @@
           <t>-1835.17</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
           <t>2026-09-24T02:40:57Z</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>MANUAL</t>
@@ -34262,7 +33046,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -34273,7 +33056,6 @@
           <t>SUPPLIER_SERVICE</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr">
         <is>
           <t>93baa3ec-84de-51bc-8495-3488293db176</t>
@@ -34316,7 +33098,6 @@
           <t>DF-WFS-HPN-26092411B</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>FT-HPN-20260924-DF11B</t>
@@ -34347,9 +33128,6 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
           <t>0.8063</t>
@@ -34365,7 +33143,6 @@
           <t>MEA</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>GR</t>
@@ -34376,22 +33153,16 @@
           <t>-2311.66</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>2026-09-24T11:12:06Z</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>MANUAL</t>
@@ -34437,7 +33208,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -34448,7 +33218,6 @@
           <t>SUPPLIER_SERVICE</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr">
         <is>
           <t>dfc60a47-8da1-5883-b030-f849c67be098</t>
@@ -34491,7 +33260,6 @@
           <t>DF-WFS-BNA-26092511C</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>FT-BNA-20260925-DF11C</t>
@@ -34522,9 +33290,6 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>0.7966</t>
@@ -34540,7 +33305,6 @@
           <t>MEA</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>GR</t>
@@ -34551,22 +33315,16 @@
           <t>-2671.80</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
           <t>2026-09-25T00:44:46Z</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>MANUAL</t>
@@ -34612,7 +33370,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -34623,7 +33380,6 @@
           <t>SUPPLIER_SERVICE</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr">
         <is>
           <t>9a32a67a-b1fe-5344-99b7-136eb2b50f40</t>
@@ -34666,7 +33422,6 @@
           <t>DF-CGA-SFO-26092512A</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>FT-SFO-20260925-DF12A</t>
@@ -34697,9 +33452,6 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
           <t>0.8035</t>
@@ -34715,7 +33467,6 @@
           <t>MEA</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>GR</t>
@@ -34726,22 +33477,16 @@
           <t>-2032.86</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>2026-09-25T06:55:23Z</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>MANUAL</t>
@@ -34787,7 +33532,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -34798,7 +33542,6 @@
           <t>RETURN_TO_SUPPLIER</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr">
         <is>
           <t>82c99cf5-b455-5854-a3c1-fbad86ade49d</t>
@@ -34841,7 +33584,6 @@
           <t>DF-WFS-BDL-26092512B</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>FT-BDL-20260925-DF12B</t>
@@ -34872,9 +33614,6 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
           <t>0.7992</t>
@@ -34890,7 +33629,6 @@
           <t>MEA</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>GR</t>
@@ -34901,22 +33639,16 @@
           <t>-1720.68</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>2026-09-25T14:22:36Z</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>MANUAL</t>
@@ -34962,7 +33694,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -34973,7 +33704,6 @@
           <t>RETURN_TO_SUPPLIER</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr">
         <is>
           <t>cfd19047-4ef2-5c1a-b9b1-c5e67d72385f</t>
@@ -35016,7 +33746,6 @@
           <t>DF-SHL-BOS-26092412C</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>FT-BOS-20260924-DF12C</t>
@@ -35047,9 +33776,6 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
           <t>0.8056</t>
@@ -35065,7 +33791,6 @@
           <t>MEA</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>GR</t>
@@ -35076,22 +33801,16 @@
           <t>-1665.98</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>2026-09-24T10:01:28Z</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>MANUAL</t>
@@ -35137,7 +33856,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -35148,7 +33866,6 @@
           <t>RETURN_TO_SUPPLIER</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr">
         <is>
           <t>174617f7-1ae7-523d-98c7-c194d383f9e5</t>
@@ -35191,7 +33908,6 @@
           <t>DF-SHL-BOS-26092613A</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>FT-BOS-20260926-DF13A</t>
@@ -35222,9 +33938,6 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
           <t>0.8095</t>
@@ -35240,7 +33953,6 @@
           <t>MEA</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>GR</t>
@@ -35251,22 +33963,16 @@
           <t>-1905.56</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>2026-09-26T13:57:34Z</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>MANUAL</t>
@@ -35312,7 +34018,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -35370,7 +34075,6 @@
           <t>DF-WFS-BOS-26092513B</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>FT-BOS-20260925-DF13B</t>
@@ -35401,9 +34105,6 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>0.8081</t>
@@ -35419,7 +34120,6 @@
           <t>MEA</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>GR</t>
@@ -35430,22 +34130,16 @@
           <t>-2738.65</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
           <t>2026-09-25T11:11:11Z</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>MANUAL</t>
@@ -35491,7 +34185,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -35549,7 +34242,6 @@
           <t>DF-BPK-LHR-26092413C</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>FT-LHR-20260924-DF13C</t>
@@ -35580,9 +34272,6 @@
           <t>LTR</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>0.8111</t>
@@ -35598,7 +34287,6 @@
           <t>MEA</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>GR</t>
@@ -35609,22 +34297,16 @@
           <t>-3104.89</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
           <t>2026-09-24T07:22:17Z</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>MANUAL</t>
@@ -35670,7 +34352,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr">
         <is>
           <t>DEFUEL</t>
@@ -36095,7 +34776,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -36111,31 +34791,21 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -36146,18 +34816,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -36168,7 +34831,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
         <is>
           <t>0</t>
@@ -36189,13 +34851,11 @@
           <t>SCENARIO 11 - defuel service charge: Payload increase after fuelling put the aircraft over MTOW; supplier defuelled the excess.</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
           <t>2026-09-27T15:00:00Z</t>
@@ -36216,27 +34876,16 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="inlineStr">
         <is>
           <t>INVOICE</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36264,7 +34913,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -36280,31 +34928,21 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -36315,18 +34953,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -36337,7 +34968,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>0</t>
@@ -36358,13 +34988,11 @@
           <t>SCENARIO 11 - defuel service charge: Aircraft change after fuelling (tail swap); fuel taken off the original tail by the supplier.</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
           <t>2026-09-27T15:00:00Z</t>
@@ -36385,27 +35013,16 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr">
         <is>
           <t>INVOICE</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36433,7 +35050,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -36449,31 +35065,21 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -36484,18 +35090,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -36506,7 +35105,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>0</t>
@@ -36527,13 +35125,11 @@
           <t>SCENARIO 11 - defuel service charge: Fuel quality hold - supplier defuelled for sampling, service charged.</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
           <t>2026-09-27T15:00:00Z</t>
@@ -36554,27 +35150,16 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr">
         <is>
           <t>INVOICE</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -36602,7 +35187,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -36618,31 +35202,21 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -36653,18 +35227,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -36675,7 +35242,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>0</t>
@@ -36696,13 +35262,11 @@
           <t>SCENARIO 12 - credit note for defuelled fuel returned to the supplier: Flight cancelled after fuelling; fuel returned to the supplier, credit note expected.</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
           <t>2026-09-27T15:00:00Z</t>
@@ -36723,20 +35287,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="inlineStr">
         <is>
           <t>CREDIT_NOTE</t>
@@ -36779,7 +35334,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -36795,31 +35349,21 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -36830,18 +35374,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -36852,7 +35389,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>0</t>
@@ -36873,13 +35409,11 @@
           <t>SCENARIO 12 - credit note for defuelled fuel returned to the supplier: Over-fuelled by the supplier against the order; excess returned for credit.</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
           <t>2026-09-27T15:00:00Z</t>
@@ -36900,20 +35434,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="inlineStr">
         <is>
           <t>CREDIT_NOTE</t>
@@ -36956,7 +35481,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -36972,31 +35496,21 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>NET30</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -37007,18 +35521,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>JB01</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
           <t>SUBMITTED</t>
@@ -37029,7 +35536,6 @@
           <t>NOT_CHECKED</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>0</t>
@@ -37050,13 +35556,11 @@
           <t>SCENARIO 12 - credit note for defuelled fuel returned to the supplier: Contamination suspected; fuel returned, part credited and part disposed (write-off).</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
           <t>2026-09-27T15:00:00Z</t>
@@ -37077,20 +35581,11 @@
           <t>SEED_B6_SCENARIO</t>
         </is>
       </c>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr">
         <is>
           <t>CREDIT_NOTE</t>
@@ -37421,10 +35916,6 @@
           <t>f28de699-2b0c-5cdc-906b-9f5ef7d23e31</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>400000</t>
@@ -37435,8 +35926,6 @@
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -37447,13 +35936,6 @@
           <t>e9df6fac-e125-58d3-a1b0-7e62a04a4ec5</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
           <t>DEFUEL_SERVICE</t>
@@ -37546,10 +36028,6 @@
           <t>660d9fd7-495d-5655-aec4-8e909652ace2</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>400000</t>
@@ -37560,8 +36038,6 @@
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -37572,13 +36048,6 @@
           <t>e458f91c-819f-5c08-b46d-e2574369cf9d</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
           <t>DEFUEL_SERVICE</t>
@@ -37671,10 +36140,6 @@
           <t>fa7578de-e328-5497-8fb9-780335a3a65f</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>400000</t>
@@ -37685,8 +36150,6 @@
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -37697,13 +36160,6 @@
           <t>f429a01a-3138-5f1a-9dc6-0536e0f09046</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
           <t>DEFUEL_SERVICE</t>
@@ -37796,10 +36252,6 @@
           <t>eb5a95f8-07c0-5472-9466-2d92f6c8e451</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>400000</t>
@@ -37810,8 +36262,6 @@
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -37822,17 +36272,11 @@
           <t>2902565d-8b21-566c-b1c9-0b443c03daf2</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
           <t>FUEL</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
           <t>FUEL</t>
@@ -37925,10 +36369,6 @@
           <t>1aea93fd-7879-50e1-b464-a9a4873e1ea8</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>400000</t>
@@ -37939,8 +36379,6 @@
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -37951,17 +36389,11 @@
           <t>3c1b763a-5003-5d98-aa1f-47b7140020e5</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
           <t>FUEL</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
           <t>FUEL</t>
@@ -38054,10 +36486,6 @@
           <t>37b68505-26f3-5325-8874-8e73fe6b0565</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>400000</t>
@@ -38068,8 +36496,6 @@
           <t>UNMATCHED</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -38080,17 +36506,11 @@
           <t>3abb4049-23b6-592e-bd4d-d982f98eea18</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
           <t>FUEL</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
           <t>FUEL</t>
@@ -38671,7 +37091,6 @@
           <t>32397.40</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38727,7 +37146,6 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>32397.40</t>
@@ -38793,7 +37211,6 @@
           <t>32397.40</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38849,7 +37266,6 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>32397.40</t>
@@ -38915,7 +37331,6 @@
           <t>32397.40</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38971,7 +37386,6 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>32397.40</t>
@@ -38999,7 +37413,6 @@
           <t>S17c</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>N645JB after B62379 2026-09-26 (IN 2026-09-26T20:20:02Z)</t>
@@ -39033,7 +37446,6 @@
           <t>6241.00</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39056,7 +37468,6 @@
           <t>S17c</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>N645JB after B62379 2026-09-26 (IN 2026-09-26T20:20:02Z)</t>
@@ -39085,7 +37496,6 @@
           <t>NO (given by the functional consultant)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>6241.00</t>
@@ -39113,7 +37523,6 @@
           <t>S17c</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>N645JB after B62379 2026-09-26 (IN 2026-09-26T20:20:02Z) - reversal</t>
@@ -39147,7 +37556,6 @@
           <t>6241.00</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39170,7 +37578,6 @@
           <t>S17c</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>N645JB after B62379 2026-09-26 (IN 2026-09-26T20:20:02Z) - reversal</t>
@@ -39199,7 +37606,6 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>6241.00</t>
@@ -39227,7 +37633,6 @@
           <t>S17c</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>N944JT after B6578 2026-09-26 (IN 2026-09-26T22:51:05Z)</t>
@@ -39261,7 +37666,6 @@
           <t>6483.69</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39284,7 +37688,6 @@
           <t>S17c</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>N944JT after B6578 2026-09-26 (IN 2026-09-26T22:51:05Z)</t>
@@ -39313,7 +37716,6 @@
           <t>NO (given by the functional consultant)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>6483.69</t>
@@ -39341,7 +37743,6 @@
           <t>S17c</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>N944JT after B6578 2026-09-26 (IN 2026-09-26T22:51:05Z) - reversal</t>
@@ -39375,7 +37776,6 @@
           <t>6483.69</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39398,7 +37798,6 @@
           <t>S17c</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>N944JT after B6578 2026-09-26 (IN 2026-09-26T22:51:05Z) - reversal</t>
@@ -39427,7 +37826,6 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>6483.69</t>
@@ -39455,7 +37853,6 @@
           <t>S17c</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>N979JT after B6924 2026-09-25 (IN 2026-09-26T03:55:58Z)</t>
@@ -39489,7 +37886,6 @@
           <t>7592.03</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39512,7 +37908,6 @@
           <t>S17c</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>N979JT after B6924 2026-09-25 (IN 2026-09-26T03:55:58Z)</t>
@@ -39541,7 +37936,6 @@
           <t>NO (given by the functional consultant)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>7592.03</t>
@@ -39569,7 +37963,6 @@
           <t>S17c</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>N979JT after B6924 2026-09-25 (IN 2026-09-26T03:55:58Z) - reversal</t>
@@ -39603,7 +37996,6 @@
           <t>7592.03</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39626,7 +38018,6 @@
           <t>S17c</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>N979JT after B6924 2026-09-25 (IN 2026-09-26T03:55:58Z) - reversal</t>
@@ -39655,7 +38046,6 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>7592.03</t>
@@ -39721,7 +38111,6 @@
           <t>5930.28</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39782,7 +38171,6 @@
           <t>196.92</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39843,7 +38231,6 @@
           <t>82.91</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39904,7 +38291,6 @@
           <t>46.64</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39960,7 +38346,6 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>6256.75</t>
@@ -40026,7 +38411,6 @@
           <t>3329.73</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40082,7 +38466,6 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>3329.73</t>
@@ -40148,7 +38531,6 @@
           <t>3329.73</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40204,7 +38586,6 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>3329.73</t>
@@ -40270,7 +38651,6 @@
           <t>73.60</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40326,7 +38706,6 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>73.60</t>
@@ -40392,7 +38771,6 @@
           <t>73.60</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40448,7 +38826,6 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>73.60</t>
@@ -40514,7 +38891,6 @@
           <t>2309.18</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40575,7 +38951,6 @@
           <t>391.83</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40631,7 +39006,6 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>2701.01</t>
@@ -44569,7 +42943,6 @@
           <t>6fe19b4a-c3bc-517b-b41e-fe50e5d83e18</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>PRIMARY</t>
@@ -44590,7 +42963,6 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>true</t>
@@ -45271,12 +43643,6 @@
           <t>1.1450</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>SAMPLE-SAMPLE-JETA-USGC-USD-L</t>
@@ -45302,8 +43668,6 @@
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>SAMPLE DATA, NOT A MARKET ASSESSMENT. Authored for the price-components demo. Do not cite, invoice or settle against it.</t>
@@ -45324,13 +43688,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
           <t>2026-09-18T20:00:00Z</t>
@@ -45388,9 +43750,6 @@
           <t>-0.26</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>SAMPLE-SAMPLE-JETA-USGC-USD-L</t>
@@ -45416,8 +43775,6 @@
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>SAMPLE DATA, NOT A MARKET ASSESSMENT. Authored for the price-components demo. Do not cite, invoice or settle against it.</t>
@@ -45438,13 +43795,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2026-09-19T20:00:00Z</t>
@@ -45502,9 +43857,6 @@
           <t>0.39</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>SAMPLE-SAMPLE-JETA-USGC-USD-L</t>
@@ -45530,8 +43882,6 @@
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>SAMPLE DATA, NOT A MARKET ASSESSMENT. Authored for the price-components demo. Do not cite, invoice or settle against it.</t>
@@ -45552,13 +43902,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
           <t>2026-09-20T20:00:00Z</t>
@@ -45616,9 +43964,6 @@
           <t>-0.37</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>SAMPLE-SAMPLE-JETA-USGC-USD-L</t>
@@ -45644,8 +43989,6 @@
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>SAMPLE DATA, NOT A MARKET ASSESSMENT. Authored for the price-components demo. Do not cite, invoice or settle against it.</t>
@@ -45666,13 +44009,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
           <t>2026-09-21T20:00:00Z</t>
@@ -45730,9 +44071,6 @@
           <t>-0.03</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>SAMPLE-SAMPLE-JETA-USGC-USD-L</t>
@@ -45758,8 +44096,6 @@
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>SAMPLE DATA, NOT A MARKET ASSESSMENT. Authored for the price-components demo. Do not cite, invoice or settle against it.</t>
@@ -45780,13 +44116,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
           <t>2026-09-22T20:00:00Z</t>
@@ -45844,9 +44178,6 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>SAMPLE-SAMPLE-JETA-USGC-USD-L</t>
@@ -45872,8 +44203,6 @@
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>SAMPLE DATA, NOT A MARKET ASSESSMENT. Authored for the price-components demo. Do not cite, invoice or settle against it.</t>
@@ -45894,13 +44223,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
           <t>2026-09-23T20:00:00Z</t>
@@ -45958,9 +44285,6 @@
           <t>0.18</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>SAMPLE-SAMPLE-JETA-USGC-USD-L</t>
@@ -45986,8 +44310,6 @@
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>SAMPLE DATA, NOT A MARKET ASSESSMENT. Authored for the price-components demo. Do not cite, invoice or settle against it.</t>
@@ -46008,13 +44330,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
           <t>2026-09-24T20:00:00Z</t>
@@ -46072,9 +44392,6 @@
           <t>0.17</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>SAMPLE-SAMPLE-JETA-USGC-USD-L</t>
@@ -46100,8 +44417,6 @@
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>SAMPLE DATA, NOT A MARKET ASSESSMENT. Authored for the price-components demo. Do not cite, invoice or settle against it.</t>
@@ -46122,13 +44437,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
           <t>2026-09-25T20:00:00Z</t>
@@ -46186,9 +44499,6 @@
           <t>-0.10</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>SAMPLE-SAMPLE-JETA-USGC-USD-L</t>
@@ -46214,8 +44524,6 @@
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>SAMPLE DATA, NOT A MARKET ASSESSMENT. Authored for the price-components demo. Do not cite, invoice or settle against it.</t>
@@ -46236,13 +44544,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
           <t>2026-09-26T20:00:00Z</t>
@@ -46300,9 +44606,6 @@
           <t>-0.24</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>SAMPLE-SAMPLE-JETA-USGC-USD-L</t>
@@ -46328,8 +44631,6 @@
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>SAMPLE DATA, NOT A MARKET ASSESSMENT. Authored for the price-components demo. Do not cite, invoice or settle against it.</t>
@@ -46350,13 +44651,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
           <t>2026-09-27T20:00:00Z</t>
@@ -46414,9 +44713,6 @@
           <t>0.10</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>SAMPLE-SAMPLE-JETA-USGC-USD-L</t>
@@ -46442,8 +44738,6 @@
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>SAMPLE DATA, NOT A MARKET ASSESSMENT. Authored for the price-components demo. Do not cite, invoice or settle against it.</t>
@@ -46464,13 +44758,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
           <t>2026-09-28T20:00:00Z</t>
@@ -46528,9 +44820,6 @@
           <t>-0.13</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>SAMPLE-SAMPLE-JETA-USGC-USD-L</t>
@@ -46556,8 +44845,6 @@
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>SAMPLE DATA, NOT A MARKET ASSESSMENT. Authored for the price-components demo. Do not cite, invoice or settle against it.</t>
@@ -46578,13 +44865,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr">
         <is>
           <t>2026-09-29T20:00:00Z</t>

--- a/docs/test-data/scenarios/JetBlue_B6_Scenario_Seed_2026-09-24_to_26.xlsx
+++ b/docs/test-data/scenarios/JetBlue_B6_Scenario_Seed_2026-09-24_to_26.xlsx
@@ -28255,12 +28255,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>16311.08</t>
+          <t>16311.06</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-1835.17</t>
+          <t>-1835.19</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -28382,7 +28382,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2867.00</t>
+          <t>-1480.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -28402,12 +28402,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>7342.23</t>
+          <t>8460.58</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-2311.66</t>
+          <t>-1193.31</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -28529,7 +28529,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3354.00</t>
+          <t>-3340.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -28549,12 +28549,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>6424.93</t>
+          <t>6428.96</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-2671.80</t>
+          <t>-2667.77</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -28696,12 +28696,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>16458.22</t>
+          <t>16456.91</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-2032.86</t>
+          <t>-2034.16</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -28823,7 +28823,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2153.00</t>
+          <t>-1110.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -28843,12 +28843,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>6727.93</t>
+          <t>7562.36</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-1720.68</t>
+          <t>-886.25</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -28990,12 +28990,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>18698.79</t>
+          <t>18698.78</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-1665.98</t>
+          <t>-1665.99</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -29137,12 +29137,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>17825.26</t>
+          <t>17827.55</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-1905.56</t>
+          <t>-1903.27</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -29222,7 +29222,7 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>BOS-FS01</t>
+          <t>BOS-TEMP</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -29269,7 +29269,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3389.00</t>
+          <t>-3060.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -29289,12 +29289,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>14783.98</t>
+          <t>15050.95</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-2738.65</t>
+          <t>-2471.68</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -29374,7 +29374,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>BOS-FS01</t>
+          <t>BOS-TEMP</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>LHR-FS01</t>
+          <t>LHR-TEMP</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -31495,7 +31495,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Defuel ticket DF-WFS-HPN-26092411B (-2867 L) and a service invoice DFS-WFS-HPN-260924B: 2867 L x 0.032/L. Aircraft change after fuelling (tail swap); fuel taken off the original tail by the supplier.</t>
+          <t>Defuel ticket DF-WFS-HPN-26092411B (-1480 L) and a service invoice DFS-WFS-HPN-260924B: 1480 L x 0.032/L. Aircraft change after fuelling (tail swap); fuel taken off the original tail by the supplier. [Seeded at 1480 L, cut from the proposed 2867 L: the tail could not spare more (DFL432).]</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -31555,7 +31555,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Defuel ticket DF-WFS-BNA-26092511C (-3354 L) and a service invoice DFS-WFS-BNA-260925C: 3354 L x 0.032/L. Fuel quality hold - supplier defuelled for sampling, service charged.</t>
+          <t>Defuel ticket DF-WFS-BNA-26092511C (-3340 L) and a service invoice DFS-WFS-BNA-260925C: 3340 L x 0.032/L. Fuel quality hold - supplier defuelled for sampling, service charged. [Seeded at 3340 L, cut from the proposed 3354 L: the tail could not spare more (DFL432).]</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -31615,7 +31615,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Defuel ticket DF-CGA-SFO-26092512A (-2530 L) and credit note CN-CGA-SFO-260925A for -2530 L at the uplift price. Flight cancelled after fuelling; fuel returned to the supplier, credit note expected.</t>
+          <t>Defuel ticket DF-CGA-SFO-26092512A (-2530 L) and credit note CN-CGA-SFO-260925A for -2530 L at the value drawn from the tail's FIFO layers. Flight cancelled after fuelling; fuel returned to the supplier, credit note expected.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -31675,7 +31675,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Defuel ticket DF-WFS-BDL-26092512B (-2153 L) and credit note CN-WFS-BDL-260925B for -2153 L at the uplift price. Over-fuelled by the supplier against the order; excess returned for credit.</t>
+          <t>Defuel ticket DF-WFS-BDL-26092512B (-1110 L) and credit note CN-WFS-BDL-260925B for -1110 L at the value drawn from the tail's FIFO layers. Over-fuelled by the supplier against the order; excess returned for credit. [Seeded at 1110 L, cut from the proposed 2153 L: the tail could not spare more (DFL432).]</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -31735,7 +31735,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Defuel ticket DF-SHL-BOS-26092412C (-2068 L) and credit note CN-SHL-BOS-260924C for -1768 L at the uplift price. Contamination suspected; fuel returned, part credited and part disposed (write-off).</t>
+          <t>Defuel ticket DF-SHL-BOS-26092412C (-2068 L) and credit note CN-SHL-BOS-260924C for -1768 L at the value drawn from the tail's FIFO layers. Contamination suspected; fuel returned, part credited and part disposed (write-off).</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -31791,12 +31791,12 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Defuel ticket DF-SHL-BOS-26092613A (-2354 L) with disposition STORAGE to BOS-FS01; no invoice. Tankering plan cancelled; fuel moved to the airline storage tank at the station.</t>
+          <t>Defuel ticket DF-SHL-BOS-26092613A (-2354 L) with disposition STORAGE to BOS-TEMP; no invoice. Tankering plan cancelled; fuel moved to the airline storage tank at the station.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Fuel moves from the tail to storage location BOS-FS01 (no supplier, no invoice). The ROB ledger takes a DEFUEL/TRANSFER out of the tail; stock moves into the storage location (S/4 transfer posting). NEEDS SCHEMA: storage location master + movement type on the ticket.</t>
+          <t>Fuel moves from the tail to storage location BOS-TEMP (no supplier, no invoice). The ROB ledger takes a DEFUEL/TRANSFER out of the tail; stock moves into the storage location (S/4 transfer posting). NEEDS SCHEMA: storage location master + movement type on the ticket.</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -31847,12 +31847,12 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Defuel ticket DF-WFS-BOS-26092513B (-3389 L) with disposition STORAGE to BOS-FS01; no invoice. Defuel ahead of a heavy check; fuel held in the airline storage tank for re-use.</t>
+          <t>Defuel ticket DF-WFS-BOS-26092513B (-3060 L) with disposition STORAGE to BOS-TEMP; no invoice. Defuel ahead of a heavy check; fuel held in the airline storage tank for re-use. [Seeded at 3060 L, cut from the proposed 3389 L: the tail could not spare more (DFL432).]</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Fuel moves from the tail to storage location BOS-FS01 (no supplier, no invoice). The ROB ledger takes a DEFUEL/TRANSFER out of the tail; stock moves into the storage location (S/4 transfer posting). NEEDS SCHEMA: storage location master + movement type on the ticket.</t>
+          <t>Fuel moves from the tail to storage location BOS-TEMP (no supplier, no invoice). The ROB ledger takes a DEFUEL/TRANSFER out of the tail; stock moves into the storage location (S/4 transfer posting). NEEDS SCHEMA: storage location master + movement type on the ticket.</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -31903,12 +31903,12 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Defuel ticket DF-BPK-LHR-26092413C (-3828 L) with disposition STORAGE to LHR-FS01; no invoice. Fuel transferred off the tail into the airline storage tank pending re-uplift.</t>
+          <t>Defuel ticket DF-BPK-LHR-26092413C (-3828 L) with disposition STORAGE to LHR-TEMP; no invoice. Fuel transferred off the tail into the airline storage tank pending re-uplift.</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Fuel moves from the tail to storage location LHR-FS01 (no supplier, no invoice). The ROB ledger takes a DEFUEL/TRANSFER out of the tail; stock moves into the storage location (S/4 transfer posting). NEEDS SCHEMA: storage location master + movement type on the ticket.</t>
+          <t>Fuel moves from the tail to storage location LHR-TEMP (no supplier, no invoice). The ROB ledger takes a DEFUEL/TRANSFER out of the tail; stock moves into the storage location (S/4 transfer posting). NEEDS SCHEMA: storage location master + movement type on the ticket.</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -32988,7 +32988,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-1835.17</t>
+          <t>-1835.19</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -33120,7 +33120,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-2867.00</t>
+          <t>-1480.00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -33150,7 +33150,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-2311.66</t>
+          <t>-1193.31</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -33282,7 +33282,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-3354.00</t>
+          <t>-3340.00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -33312,7 +33312,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-2671.80</t>
+          <t>-2667.77</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-2032.86</t>
+          <t>-2034.16</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -33606,7 +33606,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-2153.00</t>
+          <t>-1110.00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -33636,7 +33636,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-1720.68</t>
+          <t>-886.25</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -33798,7 +33798,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-1665.98</t>
+          <t>-1665.99</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -33960,7 +33960,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-1905.56</t>
+          <t>-1903.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -34030,7 +34030,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>BOS-FS01</t>
+          <t>BOS-TEMP</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -34097,7 +34097,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-3389.00</t>
+          <t>-3060.00</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -34127,7 +34127,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-2738.65</t>
+          <t>-2471.68</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -34197,7 +34197,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>BOS-FS01</t>
+          <t>BOS-TEMP</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -34364,7 +34364,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>LHR-FS01</t>
+          <t>LHR-TEMP</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -35980,7 +35980,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2867.000</t>
+          <t>1480.000</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -35995,7 +35995,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>91.74</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -36092,7 +36092,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3354.000</t>
+          <t>3340.000</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36107,7 +36107,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>107.33</t>
+          <t>106.88</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -36214,12 +36214,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.3161</t>
+          <t>1.3067</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-3329.73</t>
+          <t>-3305.92</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -36321,7 +36321,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2153.000</t>
+          <t>-1110.000</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -36331,12 +36331,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.3516</t>
+          <t>1.2666</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-2909.99</t>
+          <t>-1405.95</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-2309.18</t>
+          <t>-2309.23</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -36606,7 +36606,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BOS-FS01</t>
+          <t>BOS-TEMP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -36648,7 +36648,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LHR-FS01</t>
+          <t>LHR-TEMP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -38408,7 +38408,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3329.73</t>
+          <t>3305.92</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -38423,7 +38423,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2530 L x 1.3161</t>
+          <t>2530 L returned, valued from the tail's FIFO layers at 3305.92</t>
         </is>
       </c>
     </row>
@@ -38468,7 +38468,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3329.73</t>
+          <t>3305.92</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -38483,7 +38483,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2530 L x 1.3161</t>
+          <t>2530 L returned, valued from the tail's FIFO layers at 3305.92</t>
         </is>
       </c>
     </row>
@@ -38528,7 +38528,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3329.73</t>
+          <t>3305.92</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -38588,7 +38588,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>3329.73</t>
+          <t>3305.92</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -38888,7 +38888,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2309.18</t>
+          <t>2309.23</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -38903,7 +38903,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2068 L defuelled, 300 L disposed, at 1.3061</t>
+          <t>2068 L defuelled worth 2701.07 (FIFO layers); 1768 L credited, 300 L disposed</t>
         </is>
       </c>
     </row>
@@ -38948,7 +38948,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>391.83</t>
+          <t>391.84</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -38963,7 +38963,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2068 L defuelled, 300 L disposed, at 1.3061</t>
+          <t>2068 L defuelled worth 2701.07 (FIFO layers); 1768 L credited, 300 L disposed</t>
         </is>
       </c>
     </row>
@@ -39008,7 +39008,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2701.01</t>
+          <t>2701.07</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -39023,7 +39023,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2068 L defuelled, 300 L disposed, at 1.3061</t>
+          <t>2068 L defuelled worth 2701.07 (FIFO layers); 1768 L credited, 300 L disposed</t>
         </is>
       </c>
     </row>
